--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Capture significance" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Frame count" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Frame significance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Compute cost" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Experiment index" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="M3C2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Compute cost" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Experiment index" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8063,6 +8064,1605 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The same 6 objects x 4 methods, measured along the local surface normal instead of to the nearest point in any direction, and with no gap exclusion. Each row's registration error is its own alignment RMSE, not a constant. Read both halves: "recon" puts the core points on the reconstruction, so no pair = reconstruction surface where the reference's is not (the accuracy side); "ref" puts them on the LiDAR, so no pair = reference the reconstruction never covered (the completeness side). Outside = the reconstruction's surface sits further from the object's centre than the reference's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>source: docs/tables/m3c2_final_six.xlsx · sheet m3c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>exp_id</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>registration error (mm)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>recon: core points</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>recon: no pair (%)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>recon: |M3C2| median (cm)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>recon: |M3C2| p95 (cm)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>recon: beyond LoD95 (%)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>recon: outside the reference (%)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>ref: core points</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>ref: no pair (%)</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>ref: |M3C2| median (cm)</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>ref: |M3C2| p95 (cm)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>ref: beyond LoD95 (%)</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>ref: outside the reference (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bus_stop</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>exp_139</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23768</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15682</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bus_stop</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>exp_140</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26890</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15682</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="P6" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bus_stop</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>exp_142</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="F7" t="n">
+        <v>62241</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27</v>
+      </c>
+      <c r="K7" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15682</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bus_stop</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>exp_141</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="F8" t="n">
+        <v>224339</v>
+      </c>
+      <c r="G8" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15682</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>information_sign</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>exp_111</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4522</v>
+      </c>
+      <c r="G9" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="J9" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="P9" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>information_sign</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>exp_129</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4545</v>
+      </c>
+      <c r="G10" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="J10" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>information_sign</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>exp_126</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6208</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="P11" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>information_sign</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>exp_130</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10527</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="P12" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>exp_131</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12287</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5971</v>
+      </c>
+      <c r="M13" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>exp_132</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11498</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>66</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5971</v>
+      </c>
+      <c r="M14" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>exp_134</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14753</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>56</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5971</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="P15" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>exp_133</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="F16" t="n">
+        <v>28144</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5971</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="P16" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bollard</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>exp_143</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F17" t="n">
+        <v>975</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>811</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bollard</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>exp_144</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1093</v>
+      </c>
+      <c r="G18" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>811</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>82.40000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bollard</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>exp_146</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1313</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>811</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bollard</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>exp_145</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2062</v>
+      </c>
+      <c r="G20" t="n">
+        <v>31</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>811</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lamppost</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>exp_147</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2423</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2903</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="P21" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>lamppost</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>exp_148</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2113</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2903</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O22" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="P22" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>lamppost</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>exp_150</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7804</v>
+      </c>
+      <c r="G23" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="J23" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2903</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="P23" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>lamppost</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>exp_149</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30648</v>
+      </c>
+      <c r="G24" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="J24" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2903</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O24" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="P24" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bus_stop_sign</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>exp_135</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4356</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I25" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="J25" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3404</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="P25" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bus_stop_sign</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>exp_136</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4115</v>
+      </c>
+      <c r="G26" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3404</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O26" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="P26" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bus_stop_sign</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>exp_138</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="F27" t="n">
+        <v>16734</v>
+      </c>
+      <c r="G27" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3404</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="P27" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bus_stop_sign</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>exp_137</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24244</v>
+      </c>
+      <c r="G28" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="J28" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>58</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3404</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9290,13 +10890,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10409,29 +12009,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>exp_155</t>
+          <t>exp_131</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>information_sign_002_test_1_manual_n25</t>
+          <t>bench_004</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -10440,17 +12040,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>exp_156</t>
+          <t>exp_132</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>information_sign_002_test_1_manual_n50</t>
+          <t>bench_004</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -10459,10 +12059,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -10471,29 +12071,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>exp_158</t>
+          <t>exp_133</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>information_sign_002_test_1_manual_n100</t>
+          <t>bench_004</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
@@ -10502,29 +12102,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>exp_159</t>
+          <t>exp_134</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n15</t>
+          <t>bench_004</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
@@ -10533,29 +12133,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>exp_160</t>
+          <t>exp_135</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n30</t>
+          <t>bus_stop_sign_002</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F42" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="G42" t="n">
         <v>100</v>
@@ -10564,17 +12164,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>exp_161</t>
+          <t>exp_136</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n45</t>
+          <t>bus_stop_sign_002</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10583,10 +12183,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F43" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="G43" t="n">
         <v>100</v>
@@ -10595,17 +12195,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>exp_162</t>
+          <t>exp_137</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>information_sign_002_test_1_manual_n25</t>
+          <t>bus_stop_sign_002</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10614,10 +12214,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F44" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="G44" t="n">
         <v>100</v>
@@ -10626,29 +12226,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>exp_163</t>
+          <t>exp_138</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>information_sign_002_test_1_manual_n50</t>
+          <t>bus_stop_sign_002</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
@@ -10657,29 +12257,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>exp_164</t>
+          <t>exp_139</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>information_sign_002_test_1_manual_n100</t>
+          <t>bus_stop_002</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G46" t="n">
         <v>100</v>
@@ -10688,29 +12288,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>exp_165</t>
+          <t>exp_140</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n15</t>
+          <t>bus_stop_002</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="G47" t="n">
         <v>100</v>
@@ -10719,17 +12319,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>exp_166</t>
+          <t>exp_141</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n30</t>
+          <t>bus_stop_002</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10738,10 +12338,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -10750,29 +12350,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>exp_167</t>
+          <t>exp_142</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n45</t>
+          <t>bus_stop_002</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="G49" t="n">
         <v>100</v>
@@ -10781,29 +12381,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>exp_168</t>
+          <t>exp_143</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>bollard_003_test_1_manual_n60</t>
+          <t>bollard_003_test_1_pool69</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F50" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G50" t="n">
         <v>100</v>
@@ -10812,31 +12412,651 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>exp_144</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_pool69</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>69</v>
+      </c>
+      <c r="F51" t="n">
+        <v>69</v>
+      </c>
+      <c r="G51" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>exp_145</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_pool69</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>69</v>
+      </c>
+      <c r="F52" t="n">
+        <v>69</v>
+      </c>
+      <c r="G52" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>exp_146</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_pool69</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>69</v>
+      </c>
+      <c r="F53" t="n">
+        <v>69</v>
+      </c>
+      <c r="G53" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>exp_147</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>105</v>
+      </c>
+      <c r="F54" t="n">
+        <v>105</v>
+      </c>
+      <c r="G54" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>exp_148</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>105</v>
+      </c>
+      <c r="F55" t="n">
+        <v>105</v>
+      </c>
+      <c r="G55" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>exp_149</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>105</v>
+      </c>
+      <c r="F56" t="n">
+        <v>105</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>exp_150</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>105</v>
+      </c>
+      <c r="F57" t="n">
+        <v>105</v>
+      </c>
+      <c r="G57" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>exp_155</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>information_sign_002_test_1_manual_n25</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" t="n">
+        <v>25</v>
+      </c>
+      <c r="G58" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>exp_156</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>information_sign_002_test_1_manual_n50</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" t="n">
+        <v>50</v>
+      </c>
+      <c r="G59" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>exp_158</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>information_sign_002_test_1_manual_n100</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>exp_159</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n15</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>exp_160</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n30</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>30</v>
+      </c>
+      <c r="F62" t="n">
+        <v>30</v>
+      </c>
+      <c r="G62" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>exp_161</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n45</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>45</v>
+      </c>
+      <c r="F63" t="n">
+        <v>45</v>
+      </c>
+      <c r="G63" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>exp_162</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>information_sign_002_test_1_manual_n25</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" t="n">
+        <v>25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>exp_163</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>information_sign_002_test_1_manual_n50</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>50</v>
+      </c>
+      <c r="F65" t="n">
+        <v>50</v>
+      </c>
+      <c r="G65" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>exp_164</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>information_sign_002_test_1_manual_n100</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" t="n">
+        <v>100</v>
+      </c>
+      <c r="G66" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>exp_165</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n15</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>15</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15</v>
+      </c>
+      <c r="G67" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>exp_166</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n30</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>30</v>
+      </c>
+      <c r="F68" t="n">
+        <v>30</v>
+      </c>
+      <c r="G68" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>exp_167</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n45</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>45</v>
+      </c>
+      <c r="F69" t="n">
+        <v>45</v>
+      </c>
+      <c r="G69" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>exp_168</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>bollard_003_test_1_manual_n60</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>60</v>
+      </c>
+      <c r="F70" t="n">
+        <v>60</v>
+      </c>
+      <c r="G70" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>exp_170</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>bollard_003_test_1_manual_n60</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>hloc_colmap</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E71" t="n">
         <v>60</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F71" t="n">
         <v>60</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G71" t="n">
         <v>100</v>
       </c>
     </row>

--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Main results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Capture strategy" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Capture significance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Frame count" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Frame significance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="M3C2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Compute cost" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Experiment index" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Main significance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Capture strategy" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Capture significance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Frame count" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Frame significance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="M3C2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Compute cost" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Experiment index" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -467,11 +468,17 @@
     <col width="23" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,25 +604,55 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
+          <t>F1@3cm CI low</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>F1@3cm CI high</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>accuracy@3cm CI low</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>accuracy@3cm CI high</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>completeness@3cm CI low</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>completeness@3cm CI high</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
           <t>raw points</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>matched points (1cm voxel)</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>raw/matched ratio</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>DBSCAN mode</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>reference note</t>
         </is>
@@ -692,20 +729,38 @@
         <v>49.7</v>
       </c>
       <c r="V5" t="n">
+        <v>45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="AB5" t="n">
         <v>624826</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>118844</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AD5" t="n">
         <v>5.26</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>ft10/eps3/mp5</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
@@ -760,12 +815,30 @@
         <v>51.2</v>
       </c>
       <c r="V6" t="n">
+        <v>43</v>
+      </c>
+      <c r="W6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AB6" t="n">
         <v>789125</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AC6" t="n">
         <v>139982</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AD6" t="n">
         <v>5.64</v>
       </c>
     </row>
@@ -818,12 +891,30 @@
         <v>42.3</v>
       </c>
       <c r="V7" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1150918</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AC7" t="n">
         <v>458520</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AD7" t="n">
         <v>2.51</v>
       </c>
     </row>
@@ -876,12 +967,30 @@
         <v>55.5</v>
       </c>
       <c r="V8" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="X8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="AB8" t="n">
         <v>6995057</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AC8" t="n">
         <v>2432352</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AD8" t="n">
         <v>2.88</v>
       </c>
     </row>
@@ -956,20 +1065,38 @@
         <v>14.5</v>
       </c>
       <c r="V9" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1123433</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AC9" t="n">
         <v>36738</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AD9" t="n">
         <v>30.58</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>incomplete reference: only the upper ~2/3 of the pole height and one side were scanned — comparison is only valid in that region (not a scale/rotation error)</t>
         </is>
@@ -1024,12 +1151,30 @@
         <v>18.2</v>
       </c>
       <c r="V10" t="n">
+        <v>79</v>
+      </c>
+      <c r="W10" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="X10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1064834</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AC10" t="n">
         <v>37804</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AD10" t="n">
         <v>28.17</v>
       </c>
     </row>
@@ -1082,12 +1227,30 @@
         <v>11.5</v>
       </c>
       <c r="V11" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AB11" t="n">
         <v>734656</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AC11" t="n">
         <v>70153</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AD11" t="n">
         <v>10.47</v>
       </c>
     </row>
@@ -1140,12 +1303,30 @@
         <v>30</v>
       </c>
       <c r="V12" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>99</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AB12" t="n">
         <v>3334257</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AC12" t="n">
         <v>161957</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AD12" t="n">
         <v>20.59</v>
       </c>
     </row>
@@ -1220,20 +1401,38 @@
         <v>24.8</v>
       </c>
       <c r="V13" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>68</v>
+      </c>
+      <c r="X13" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1520520</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AC13" t="n">
         <v>115064</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AD13" t="n">
         <v>13.21</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>ft5/eps3/mp2</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>incomplete reference: the bench's backrest (rear side) and legs are missing</t>
         </is>
@@ -1288,12 +1487,30 @@
         <v>36.2</v>
       </c>
       <c r="V14" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1462675</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AC14" t="n">
         <v>103983</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AD14" t="n">
         <v>14.07</v>
       </c>
     </row>
@@ -1346,12 +1563,30 @@
         <v>29.7</v>
       </c>
       <c r="V15" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="X15" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AB15" t="n">
         <v>804316</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AC15" t="n">
         <v>136786</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AD15" t="n">
         <v>5.88</v>
       </c>
     </row>
@@ -1404,12 +1639,30 @@
         <v>32.5</v>
       </c>
       <c r="V16" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>68</v>
+      </c>
+      <c r="X16" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="AB16" t="n">
         <v>6726594</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AC16" t="n">
         <v>359926</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AD16" t="n">
         <v>18.69</v>
       </c>
     </row>
@@ -1484,20 +1737,38 @@
         <v>16.1</v>
       </c>
       <c r="V17" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>77</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="AB17" t="n">
         <v>214105</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AC17" t="n">
         <v>6021</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AD17" t="n">
         <v>35.56</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>incomplete reference: only one side was scanned (~90° sector missing) — the missing side is handled via gap detection (DBSCAN)</t>
         </is>
@@ -1552,12 +1823,30 @@
         <v>10.9</v>
       </c>
       <c r="V18" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AB18" t="n">
         <v>308184</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AC18" t="n">
         <v>7106</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AD18" t="n">
         <v>43.37</v>
       </c>
     </row>
@@ -1610,12 +1899,30 @@
         <v>6</v>
       </c>
       <c r="V19" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>89</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB19" t="n">
         <v>533608</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AC19" t="n">
         <v>14002</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AD19" t="n">
         <v>38.11</v>
       </c>
     </row>
@@ -1668,12 +1975,30 @@
         <v>8.6</v>
       </c>
       <c r="V20" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB20" t="n">
         <v>3697595</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AC20" t="n">
         <v>28592</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AD20" t="n">
         <v>129.32</v>
       </c>
     </row>
@@ -1748,20 +2073,38 @@
         <v>9.800000000000001</v>
       </c>
       <c r="V21" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="X21" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="AB21" t="n">
         <v>133185</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AC21" t="n">
         <v>18583</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AD21" t="n">
         <v>7.17</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -1816,12 +2159,30 @@
         <v>11.5</v>
       </c>
       <c r="V22" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="X22" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AB22" t="n">
         <v>59502</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AC22" t="n">
         <v>10543</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AD22" t="n">
         <v>5.64</v>
       </c>
     </row>
@@ -1874,12 +2235,30 @@
         <v>34</v>
       </c>
       <c r="V23" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="AB23" t="n">
         <v>177102</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AC23" t="n">
         <v>46577</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AD23" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1932,12 +2311,30 @@
         <v>41.6</v>
       </c>
       <c r="V24" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AB24" t="n">
         <v>293168</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AC24" t="n">
         <v>152549</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AD24" t="n">
         <v>1.92</v>
       </c>
     </row>
@@ -2012,20 +2409,38 @@
         <v>27.2</v>
       </c>
       <c r="V25" t="n">
+        <v>65</v>
+      </c>
+      <c r="W25" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AB25" t="n">
         <v>327676</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AC25" t="n">
         <v>29266</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AD25" t="n">
         <v>11.2</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -2080,12 +2495,30 @@
         <v>34.9</v>
       </c>
       <c r="V26" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AB26" t="n">
         <v>261293</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AC26" t="n">
         <v>23147</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AD26" t="n">
         <v>11.29</v>
       </c>
     </row>
@@ -2138,12 +2571,30 @@
         <v>27.2</v>
       </c>
       <c r="V27" t="n">
+        <v>41</v>
+      </c>
+      <c r="W27" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="AB27" t="n">
         <v>569403</v>
       </c>
-      <c r="W27" t="n">
+      <c r="AC27" t="n">
         <v>130311</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AD27" t="n">
         <v>4.37</v>
       </c>
     </row>
@@ -2196,12 +2647,30 @@
         <v>37</v>
       </c>
       <c r="V28" t="n">
+        <v>51</v>
+      </c>
+      <c r="W28" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="X28" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2881563</v>
       </c>
-      <c r="W28" t="n">
+      <c r="AC28" t="n">
         <v>322936</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AD28" t="n">
         <v>8.92</v>
       </c>
     </row>
@@ -2211,6 +2680,1197 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pairwise F1@3cm differences between methods on the same object, block bootstrap. Unpaired: the four reconstructions of an object share no frames. A CI spanning 0 means the two methods are not distinguishable on that object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>source: docs/tables/summary_all_objects_accuracy_f1_EN.xlsx · sheet significance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>object_id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>method A</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>method B</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ΔF1@3cm (pp)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>95% CI low</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>95% CI high</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>resolvable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F34" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3395,7 +5055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3842,7 +5502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5817,7 +7477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8058,7 +9718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9657,7 +11317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10890,7 +12550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>alignment RMSE (mm)</t>
+          <t>alignment RMSE (cm)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         <v>4.03</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>1.93</v>
       </c>
       <c r="K5" t="n">
         <v>50.6</v>
@@ -809,7 +809,7 @@
         <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>19.75</v>
+        <v>1.98</v>
       </c>
       <c r="K6" t="n">
         <v>42.8</v>
@@ -894,7 +894,7 @@
         <v>1.31</v>
       </c>
       <c r="J7" t="n">
-        <v>19.08</v>
+        <v>1.91</v>
       </c>
       <c r="K7" t="n">
         <v>38.7</v>
@@ -979,7 +979,7 @@
         <v>0.71</v>
       </c>
       <c r="J8" t="n">
-        <v>20.04</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>18.7</v>
@@ -1086,7 +1086,7 @@
         <v>0.58</v>
       </c>
       <c r="J9" t="n">
-        <v>14.82</v>
+        <v>1.48</v>
       </c>
       <c r="K9" t="n">
         <v>40.5</v>
@@ -1181,7 +1181,7 @@
         <v>0.91</v>
       </c>
       <c r="J10" t="n">
-        <v>15.7</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="n">
         <v>35.6</v>
@@ -1266,7 +1266,7 @@
         <v>0.64</v>
       </c>
       <c r="J11" t="n">
-        <v>16.09</v>
+        <v>1.61</v>
       </c>
       <c r="K11" t="n">
         <v>42.3</v>
@@ -1351,7 +1351,7 @@
         <v>0.63</v>
       </c>
       <c r="J12" t="n">
-        <v>19.77</v>
+        <v>1.98</v>
       </c>
       <c r="K12" t="n">
         <v>24.2</v>
@@ -1458,7 +1458,7 @@
         <v>1.69</v>
       </c>
       <c r="J13" t="n">
-        <v>19.87</v>
+        <v>1.99</v>
       </c>
       <c r="K13" t="n">
         <v>56.2</v>
@@ -1553,7 +1553,7 @@
         <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>21.7</v>
+        <v>2.17</v>
       </c>
       <c r="K14" t="n">
         <v>50.5</v>
@@ -1638,7 +1638,7 @@
         <v>1.48</v>
       </c>
       <c r="J15" t="n">
-        <v>19.55</v>
+        <v>1.96</v>
       </c>
       <c r="K15" t="n">
         <v>56.1</v>
@@ -1723,7 +1723,7 @@
         <v>1.11</v>
       </c>
       <c r="J16" t="n">
-        <v>20.86</v>
+        <v>2.09</v>
       </c>
       <c r="K16" t="n">
         <v>39.5</v>
@@ -1830,7 +1830,7 @@
         <v>1.21</v>
       </c>
       <c r="J17" t="n">
-        <v>12.68</v>
+        <v>1.27</v>
       </c>
       <c r="K17" t="n">
         <v>68.2</v>
@@ -1925,7 +1925,7 @@
         <v>0.89</v>
       </c>
       <c r="J18" t="n">
-        <v>12.19</v>
+        <v>1.22</v>
       </c>
       <c r="K18" t="n">
         <v>69.59999999999999</v>
@@ -2010,7 +2010,7 @@
         <v>0.61</v>
       </c>
       <c r="J19" t="n">
-        <v>12.82</v>
+        <v>1.28</v>
       </c>
       <c r="K19" t="n">
         <v>72.2</v>
@@ -2095,7 +2095,7 @@
         <v>0.63</v>
       </c>
       <c r="J20" t="n">
-        <v>14.65</v>
+        <v>1.47</v>
       </c>
       <c r="K20" t="n">
         <v>64</v>
@@ -2202,7 +2202,7 @@
         <v>1.23</v>
       </c>
       <c r="J21" t="n">
-        <v>11.59</v>
+        <v>1.16</v>
       </c>
       <c r="K21" t="n">
         <v>96.59999999999999</v>
@@ -2297,7 +2297,7 @@
         <v>1.65</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="n">
         <v>91.7</v>
@@ -2382,7 +2382,7 @@
         <v>1.32</v>
       </c>
       <c r="J23" t="n">
-        <v>16.84</v>
+        <v>1.68</v>
       </c>
       <c r="K23" t="n">
         <v>44.5</v>
@@ -2467,7 +2467,7 @@
         <v>1.17</v>
       </c>
       <c r="J24" t="n">
-        <v>17.59</v>
+        <v>1.76</v>
       </c>
       <c r="K24" t="n">
         <v>12.3</v>
@@ -2574,7 +2574,7 @@
         <v>1.88</v>
       </c>
       <c r="J25" t="n">
-        <v>17.77</v>
+        <v>1.78</v>
       </c>
       <c r="K25" t="n">
         <v>58.8</v>
@@ -2669,7 +2669,7 @@
         <v>2.16</v>
       </c>
       <c r="J26" t="n">
-        <v>16.59</v>
+        <v>1.66</v>
       </c>
       <c r="K26" t="n">
         <v>52.7</v>
@@ -2754,7 +2754,7 @@
         <v>1.3</v>
       </c>
       <c r="J27" t="n">
-        <v>17.87</v>
+        <v>1.79</v>
       </c>
       <c r="K27" t="n">
         <v>28.6</v>
@@ -2839,7 +2839,7 @@
         <v>0.58</v>
       </c>
       <c r="J28" t="n">
-        <v>18.17</v>
+        <v>1.82</v>
       </c>
       <c r="K28" t="n">
         <v>35.5</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>inlier RMSE@3cm (mm)</t>
+          <t>inlier RMSE@3cm (cm)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -8305,7 +8305,7 @@
         <v>1.854</v>
       </c>
       <c r="S5" t="n">
-        <v>13.01</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
         <v>100</v>
@@ -8389,7 +8389,7 @@
         <v>1.688</v>
       </c>
       <c r="S6" t="n">
-        <v>11.1</v>
+        <v>1.11</v>
       </c>
       <c r="T6" t="n">
         <v>100</v>
@@ -8473,7 +8473,7 @@
         <v>1.584</v>
       </c>
       <c r="S7" t="n">
-        <v>14.18</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
         <v>100</v>
@@ -8557,7 +8557,7 @@
         <v>0.53</v>
       </c>
       <c r="S8" t="n">
-        <v>12.73</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
         <v>100</v>
@@ -8641,7 +8641,7 @@
         <v>0.641</v>
       </c>
       <c r="S9" t="n">
-        <v>12.09</v>
+        <v>1.21</v>
       </c>
       <c r="T9" t="n">
         <v>100</v>
@@ -8725,7 +8725,7 @@
         <v>0.897</v>
       </c>
       <c r="S10" t="n">
-        <v>13.81</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
         <v>100</v>
@@ -8809,7 +8809,7 @@
         <v>1.948</v>
       </c>
       <c r="S11" t="n">
-        <v>17.37</v>
+        <v>1.74</v>
       </c>
       <c r="T11" t="n">
         <v>100</v>
@@ -8893,7 +8893,7 @@
         <v>6.463</v>
       </c>
       <c r="S12" t="n">
-        <v>19.45</v>
+        <v>1.95</v>
       </c>
       <c r="T12" t="n">
         <v>95.8</v>
@@ -8977,7 +8977,7 @@
         <v>1.686</v>
       </c>
       <c r="S13" t="n">
-        <v>19.63</v>
+        <v>1.96</v>
       </c>
       <c r="T13" t="n">
         <v>100</v>
@@ -9061,7 +9061,7 @@
         <v>0.577</v>
       </c>
       <c r="S14" t="n">
-        <v>17.25</v>
+        <v>1.73</v>
       </c>
       <c r="T14" t="n">
         <v>100</v>
@@ -9145,7 +9145,7 @@
         <v>2.841</v>
       </c>
       <c r="S15" t="n">
-        <v>19.12</v>
+        <v>1.91</v>
       </c>
       <c r="T15" t="n">
         <v>100</v>
@@ -9229,7 +9229,7 @@
         <v>0.716</v>
       </c>
       <c r="S16" t="n">
-        <v>16.49</v>
+        <v>1.65</v>
       </c>
       <c r="T16" t="n">
         <v>100</v>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>inlier RMSE@3cm (mm)</t>
+          <t>inlier RMSE@3cm (cm)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -9926,7 +9926,7 @@
         <v>6.495</v>
       </c>
       <c r="J5" t="n">
-        <v>13.3</v>
+        <v>1.33</v>
       </c>
       <c r="K5" t="n">
         <v>88.47</v>
@@ -10015,7 +10015,7 @@
         <v>1.678</v>
       </c>
       <c r="J6" t="n">
-        <v>12.14</v>
+        <v>1.21</v>
       </c>
       <c r="K6" t="n">
         <v>91.39</v>
@@ -10104,7 +10104,7 @@
         <v>1.523</v>
       </c>
       <c r="J7" t="n">
-        <v>13.11</v>
+        <v>1.31</v>
       </c>
       <c r="K7" t="n">
         <v>89.8</v>
@@ -10193,7 +10193,7 @@
         <v>1.336</v>
       </c>
       <c r="J8" t="n">
-        <v>13.35</v>
+        <v>1.33</v>
       </c>
       <c r="K8" t="n">
         <v>92.95</v>
@@ -10282,7 +10282,7 @@
         <v>0.493</v>
       </c>
       <c r="J9" t="n">
-        <v>11.98</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
         <v>90.42</v>
@@ -10371,7 +10371,7 @@
         <v>0.701</v>
       </c>
       <c r="J10" t="n">
-        <v>12.2</v>
+        <v>1.22</v>
       </c>
       <c r="K10" t="n">
         <v>90.75</v>
@@ -10460,7 +10460,7 @@
         <v>0.66</v>
       </c>
       <c r="J11" t="n">
-        <v>12.33</v>
+        <v>1.23</v>
       </c>
       <c r="K11" t="n">
         <v>90.84999999999999</v>
@@ -10549,7 +10549,7 @@
         <v>0.678</v>
       </c>
       <c r="J12" t="n">
-        <v>12.68</v>
+        <v>1.27</v>
       </c>
       <c r="K12" t="n">
         <v>90.62</v>
@@ -10638,7 +10638,7 @@
         <v>1.546</v>
       </c>
       <c r="J13" t="n">
-        <v>16.31</v>
+        <v>1.63</v>
       </c>
       <c r="K13" t="n">
         <v>74.14</v>
@@ -10727,7 +10727,7 @@
         <v>0.751</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
         <v>80.08</v>
@@ -10816,7 +10816,7 @@
         <v>0.577</v>
       </c>
       <c r="J15" t="n">
-        <v>14.82</v>
+        <v>1.48</v>
       </c>
       <c r="K15" t="n">
         <v>81.51000000000001</v>
@@ -10905,7 +10905,7 @@
         <v>0.755</v>
       </c>
       <c r="J16" t="n">
-        <v>14.95</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
         <v>82.53</v>
@@ -10994,7 +10994,7 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>19.14</v>
+        <v>1.91</v>
       </c>
       <c r="K17" t="n">
         <v>74.37</v>
@@ -11083,7 +11083,7 @@
         <v>0.825</v>
       </c>
       <c r="J18" t="n">
-        <v>17.26</v>
+        <v>1.73</v>
       </c>
       <c r="K18" t="n">
         <v>72.98</v>
@@ -11172,7 +11172,7 @@
         <v>0.792</v>
       </c>
       <c r="J19" t="n">
-        <v>17.48</v>
+        <v>1.75</v>
       </c>
       <c r="K19" t="n">
         <v>75.54000000000001</v>
@@ -11261,7 +11261,7 @@
         <v>0.661</v>
       </c>
       <c r="J20" t="n">
-        <v>17.69</v>
+        <v>1.77</v>
       </c>
       <c r="K20" t="n">
         <v>72.62</v>
@@ -11350,7 +11350,7 @@
         <v>0.718</v>
       </c>
       <c r="J21" t="n">
-        <v>17.28</v>
+        <v>1.73</v>
       </c>
       <c r="K21" t="n">
         <v>75.23999999999999</v>
@@ -11439,7 +11439,7 @@
         <v>0.716</v>
       </c>
       <c r="J22" t="n">
-        <v>19.29</v>
+        <v>1.93</v>
       </c>
       <c r="K22" t="n">
         <v>73.36</v>
@@ -11528,7 +11528,7 @@
         <v>0.642</v>
       </c>
       <c r="J23" t="n">
-        <v>16.09</v>
+        <v>1.61</v>
       </c>
       <c r="K23" t="n">
         <v>79.92</v>
@@ -11617,7 +11617,7 @@
         <v>0.577</v>
       </c>
       <c r="J24" t="n">
-        <v>16.44</v>
+        <v>1.64</v>
       </c>
       <c r="K24" t="n">
         <v>75.92</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>registration error (mm)</t>
+          <t>registration error (cm)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19.28</v>
+        <v>1.93</v>
       </c>
       <c r="F5" t="n">
         <v>23768</v>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19.75</v>
+        <v>1.98</v>
       </c>
       <c r="F6" t="n">
         <v>26890</v>
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.08</v>
+        <v>1.91</v>
       </c>
       <c r="F7" t="n">
         <v>62241</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20.04</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>224339</v>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14.82</v>
+        <v>1.48</v>
       </c>
       <c r="F9" t="n">
         <v>4522</v>
@@ -14374,7 +14374,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>15.7</v>
+        <v>1.57</v>
       </c>
       <c r="F10" t="n">
         <v>4545</v>
@@ -14435,7 +14435,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16.09</v>
+        <v>1.61</v>
       </c>
       <c r="F11" t="n">
         <v>6208</v>
@@ -14496,7 +14496,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19.77</v>
+        <v>1.98</v>
       </c>
       <c r="F12" t="n">
         <v>10527</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19.87</v>
+        <v>1.99</v>
       </c>
       <c r="F13" t="n">
         <v>12287</v>
@@ -14618,7 +14618,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21.7</v>
+        <v>2.17</v>
       </c>
       <c r="F14" t="n">
         <v>11498</v>
@@ -14679,7 +14679,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19.55</v>
+        <v>1.96</v>
       </c>
       <c r="F15" t="n">
         <v>14753</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>20.86</v>
+        <v>2.09</v>
       </c>
       <c r="F16" t="n">
         <v>28144</v>
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.68</v>
+        <v>1.27</v>
       </c>
       <c r="F17" t="n">
         <v>975</v>
@@ -14862,7 +14862,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.19</v>
+        <v>1.22</v>
       </c>
       <c r="F18" t="n">
         <v>1093</v>
@@ -14923,7 +14923,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12.82</v>
+        <v>1.28</v>
       </c>
       <c r="F19" t="n">
         <v>1313</v>
@@ -14984,7 +14984,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14.65</v>
+        <v>1.47</v>
       </c>
       <c r="F20" t="n">
         <v>2062</v>
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.59</v>
+        <v>1.16</v>
       </c>
       <c r="F21" t="n">
         <v>2423</v>
@@ -15106,7 +15106,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="F22" t="n">
         <v>2113</v>
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16.84</v>
+        <v>1.68</v>
       </c>
       <c r="F23" t="n">
         <v>7804</v>
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17.59</v>
+        <v>1.76</v>
       </c>
       <c r="F24" t="n">
         <v>30648</v>
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17.77</v>
+        <v>1.78</v>
       </c>
       <c r="F25" t="n">
         <v>4356</v>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16.59</v>
+        <v>1.66</v>
       </c>
       <c r="F26" t="n">
         <v>4115</v>
@@ -15411,7 +15411,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>17.87</v>
+        <v>1.79</v>
       </c>
       <c r="F27" t="n">
         <v>16734</v>
@@ -15472,7 +15472,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18.17</v>
+        <v>1.82</v>
       </c>
       <c r="F28" t="n">
         <v>24244</v>
@@ -16774,7 +16774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IoU at 2, 3, 5 and 10 cm for every row. 5 cm is the primary size, and it is clamped from both sides rather than chosen: at least ~4 cm so that a surface voxel holds several reference points (worst median spacing is 2.00 cm, on the bench) and so that a 2 cm alignment error cannot shift occupancy by a whole voxel (worst inlier RMSE 21.7 mm); at most 5 cm so the lamppost, 15.5 cm across, still spans three voxels. The two ends are reported to show what happens there, not as results - 2 cm sits below both lower bounds and drops recall for every method at once, which is an artefact of how the reference was sampled; at 10 cm the lamppost and the sign's pole stop resolving and IoU measures bounding volume rather than shape. The per-row note column repeats this.</t>
+          <t>IoU at 2, 3, 5 and 10 cm for every row. 5 cm is the primary size, and it is clamped from both sides rather than chosen: at least ~4 cm so that a surface voxel holds several reference points (worst median spacing is 2.00 cm, on the bench) and so that a 2 cm alignment error cannot shift occupancy by a whole voxel (worst inlier RMSE 2.17 cm); at most 5 cm so the lamppost, 15.5 cm across, still spans three voxels. The two ends are reported to show what happens there, not as results - 2 cm sits below both lower bounds and drops recall for every method at once, which is an artefact of how the reference was sampled; at 10 cm the lamppost and the sign's pole stop resolving and IoU measures bounding volume rather than shape. The per-row note column repeats this.</t>
         </is>
       </c>
     </row>

--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Does not belong in chapter 5: IoU matches the F1@3cm ordering exactly on 2 of 6 objects, and every reordering it produces on the other 4 fails on inspection - see below. No new conclusion. Mention it in the methodology as an alternative that was considered, and leave it out of the results. The voxel sweep does reorder methods beyond the grid noise on bench_004, but singles out the same method ΔF1@10-3 already singles out there, so it restates the existing table rather than adding to it. Reorderings that were found but are smaller than the grid-origin noise, and so decide nothing: bench_004, bollard_003, bus_stop_002, information_sign_002. Caveat to state either way: the method ordering does not survive the grid-origin shift on bus_stop_002, information_sign_002, bench_004, bollard_003, so IoU cannot separate those methods at this voxel size.</t>
+          <t>IoU adds no ordering of its own: it matches the F1@3cm ordering exactly on 2 of 6 objects, and every reordering it produces on the other 4 fails on inspection - see below. So IoU confirms the F1 ordering rather than competing with it: a density-free check on the primary measure, not a second source of conclusions. The voxel sweep does reorder methods beyond the grid noise on bench_004, but singles out the same method ΔF1@10-3 already singles out there, so it restates the existing table rather than adding to it. Reorderings that were found but are smaller than the grid-origin noise, and so decide nothing: bench_004, bollard_003, bus_stop_002, information_sign_002. Caveat to state either way: the method ordering does not survive the grid-origin shift on bus_stop_002, information_sign_002, bench_004, bollard_003, so IoU cannot separate those methods at this voxel size.</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8097,11 +8097,12 @@
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8217,25 +8218,30 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
+          <t>images in</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>reg-rate (%)</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>points raw</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>points density-matched</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>excluded as gap</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>DBSCAN (ft/eps/mp)</t>
         </is>
@@ -8308,18 +8314,21 @@
         <v>1.3</v>
       </c>
       <c r="T5" t="n">
+        <v>44</v>
+      </c>
+      <c r="U5" t="n">
         <v>100</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>105933</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>3847</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>754</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8392,18 +8401,21 @@
         <v>1.11</v>
       </c>
       <c r="T6" t="n">
+        <v>44</v>
+      </c>
+      <c r="U6" t="n">
         <v>100</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>36609</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>2715</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>419</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8476,18 +8488,21 @@
         <v>1.42</v>
       </c>
       <c r="T7" t="n">
+        <v>44</v>
+      </c>
+      <c r="U7" t="n">
         <v>100</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>167287</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>5592</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>1295</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8560,18 +8575,21 @@
         <v>1.27</v>
       </c>
       <c r="T8" t="n">
+        <v>44</v>
+      </c>
+      <c r="U8" t="n">
         <v>100</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>441241</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>16196</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>4072</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8644,18 +8662,21 @@
         <v>1.21</v>
       </c>
       <c r="T9" t="n">
+        <v>44</v>
+      </c>
+      <c r="U9" t="n">
         <v>100</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>750396</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>12872</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>2676</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8728,18 +8749,21 @@
         <v>1.38</v>
       </c>
       <c r="T10" t="n">
+        <v>44</v>
+      </c>
+      <c r="U10" t="n">
         <v>100</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>482225</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>13029</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>2580</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8812,18 +8836,21 @@
         <v>1.74</v>
       </c>
       <c r="T11" t="n">
+        <v>48</v>
+      </c>
+      <c r="U11" t="n">
         <v>100</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>547654</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>25404</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>14198</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8896,18 +8923,21 @@
         <v>1.95</v>
       </c>
       <c r="T12" t="n">
+        <v>48</v>
+      </c>
+      <c r="U12" t="n">
         <v>95.8</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>801528</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>19421</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>15582</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -8980,18 +9010,21 @@
         <v>1.96</v>
       </c>
       <c r="T13" t="n">
+        <v>48</v>
+      </c>
+      <c r="U13" t="n">
         <v>100</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>716317</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>35676</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>21922</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -9064,18 +9097,21 @@
         <v>1.73</v>
       </c>
       <c r="T14" t="n">
+        <v>48</v>
+      </c>
+      <c r="U14" t="n">
         <v>100</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>540530</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>75146</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>36753</v>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -9148,18 +9184,21 @@
         <v>1.91</v>
       </c>
       <c r="T15" t="n">
+        <v>48</v>
+      </c>
+      <c r="U15" t="n">
         <v>100</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>1129311</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>70386</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>49235</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -9232,18 +9271,21 @@
         <v>1.65</v>
       </c>
       <c r="T16" t="n">
+        <v>48</v>
+      </c>
+      <c r="U16" t="n">
         <v>100</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>484330</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>59039</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>28083</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>

--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
+          <t>incomplete reference: the bus shelter's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
       </c>
     </row>
